--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512450_1ºBA1ºBBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512450_1ºBA1ºBBFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2222</v>
+        <v>2.1947</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7692</v>
+        <v>1.7636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.453</v>
+        <v>0.4311</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9651</v>
+        <v>0.9116</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1946</v>
+        <v>-1.2768</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1597</v>
+        <v>2.1884</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5673</v>
+        <v>1.6851</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1581</v>
+        <v>-0.1308</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7255</v>
+        <v>1.816</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6022</v>
+        <v>-0.7735</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0364</v>
+        <v>-1.146</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4342</v>
+        <v>0.3725</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.731</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0027</v>
+        <v>0.8048</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2855</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6338</v>
+        <v>0.2082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9286</v>
+        <v>1.2547</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2947</v>
+        <v>-1.0464</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8048</v>
+        <v>-0.7832</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4155</v>
+        <v>-0.4203</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3893</v>
+        <v>-0.3629</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3889</v>
+        <v>-0.2281</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9633</v>
+        <v>1.052</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3522</v>
+        <v>-1.2801</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4159</v>
+        <v>-0.5551</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3789</v>
+        <v>-1.4723</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9629</v>
+        <v>0.9172</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0385</v>
+        <v>1.602</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5181</v>
+        <v>0.6248</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5205</v>
+        <v>0.9771</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0901</v>
+        <v>-0.0824</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5854</v>
+        <v>-0.7909</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4953</v>
+        <v>0.7085</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.1977</v>
+        <v>-2.2103</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9823</v>
+        <v>-0.9832</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2154</v>
+        <v>-1.2271</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2324</v>
+        <v>-1.1407</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0036</v>
+        <v>0.0668</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.236</v>
+        <v>-1.2074</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9653</v>
+        <v>-1.0696</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9859</v>
+        <v>-1.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6272</v>
+        <v>0.6869</v>
       </c>
       <c r="T4" t="n">
-        <v>0.647</v>
+        <v>0.3498</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0198</v>
+        <v>0.3371</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1953</v>
+        <v>-0.0959</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2863</v>
+        <v>0.3475</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.4816</v>
+        <v>-0.4434</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1818</v>
+        <v>-1.1453</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4578</v>
+        <v>-3.1179</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.6396</v>
+        <v>1.9727</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3051</v>
+        <v>0.7822</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5011</v>
+        <v>-1.0904</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.196</v>
+        <v>1.8726</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4869</v>
+        <v>-1.9275</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0433</v>
+        <v>-2.0276</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4436</v>
+        <v>0.1001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4004</v>
+        <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8074</v>
+        <v>0.8546</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0027</v>
+        <v>0.539</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1953</v>
+        <v>0.3156</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7794</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9791</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3329</v>
+        <v>-0.4539</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0263</v>
+        <v>2.0271</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3066</v>
+        <v>-2.4809</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0882</v>
+        <v>-0.6589</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.0617</v>
+        <v>0.3156</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9734</v>
+        <v>-0.9744</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6493</v>
+        <v>1.8253</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1543</v>
+        <v>1.7037</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8036</v>
+        <v>0.1216</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7375</v>
+        <v>-2.4841</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9074</v>
+        <v>-1.3881</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1699</v>
+        <v>-1.096</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2003</v>
+        <v>0.3895</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5553</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3247</v>
+        <v>-0.3572</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2306</v>
+        <v>-0.3862</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8148</v>
+        <v>-0.8706</v>
       </c>
       <c r="E7" t="n">
-        <v>1.719</v>
+        <v>1.9505</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5338</v>
+        <v>-2.8211</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5924</v>
+        <v>-1.2097</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3381</v>
+        <v>1.465</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9305</v>
+        <v>-2.6747</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7795</v>
+        <v>1.4323</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6595</v>
+        <v>2.5992</v>
       </c>
       <c r="L7" t="n">
-        <v>0.12</v>
+        <v>-1.1669</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3719</v>
+        <v>-2.642</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3214</v>
+        <v>-1.1342</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0505</v>
+        <v>-1.5078</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4001</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1421</v>
+        <v>0.0849</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.4061</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.3212</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5196</v>
+        <v>0.8384</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5196</v>
+        <v>2.0595</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. BOONYASITH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0088</v>
+        <v>-2.1208</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2551</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2638</v>
+        <v>-2.7987</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-2.5572</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6885</v>
+        <v>-0.2961</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0731</v>
+        <v>-2.2611</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6418</v>
+        <v>0.5322</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>0.621</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6018</v>
+        <v>-0.0888</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2572</v>
+        <v>-3.0894</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7285</v>
+        <v>-0.9171</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-2.1723</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2001</v>
+        <v>0.7789</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3937</v>
+        <v>-0.8694</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3867</v>
+        <v>-0.3812</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0069</v>
+        <v>-0.4882</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1998</v>
+        <v>1.5005</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BOONYASITH</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5235</v>
+        <v>-2.1249</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1394</v>
+        <v>0.3024</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.663</v>
+        <v>-2.4273</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5827</v>
+        <v>-0.6319</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3068</v>
+        <v>-0.7195</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2759</v>
+        <v>0.0876</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3892</v>
+        <v>0.6734</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5435</v>
+        <v>0.0411</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1543</v>
+        <v>0.6323</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9719</v>
+        <v>-1.3052</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.7605</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1216</v>
+        <v>-0.5447</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8002</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2003</v>
+        <v>-0.4668</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.709</v>
+        <v>-0.371</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4913</v>
+        <v>-0.0958</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4596</v>
+        <v>-1.2211</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4596</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3715</v>
+        <v>-3.3458</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7075</v>
+        <v>-2.5343</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.664</v>
+        <v>-0.8115</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3777</v>
+        <v>-2.3945</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7154</v>
+        <v>-0.7282</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6622</v>
+        <v>-1.6663</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.256</v>
+        <v>-1.2274</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1217</v>
+        <v>-1.1671</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0574</v>
+        <v>-0.0842</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0642</v>
+        <v>-1.0829</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5937</v>
+        <v>-0.5618</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4512</v>
+        <v>-0.3332</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1425</v>
+        <v>-0.2287</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8098</v>
+        <v>-3.5956</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8032</v>
+        <v>-4.3069</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.7113</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7997</v>
+        <v>0.8305</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5704</v>
+        <v>0.6297</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2293</v>
+        <v>0.2008</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1651</v>
+        <v>1.2896</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0851</v>
+        <v>1.2086</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3654</v>
+        <v>-0.4591</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5147</v>
+        <v>-0.5789</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.0017</v>
+        <v>-5.8421</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.7217</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0334</v>
+        <v>0.2455</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6183</v>
+        <v>0.4762</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.2907</v>
+        <v>-10.287</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0248</v>
+        <v>0.6916000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.2658</v>
+        <v>-10.9784</v>
       </c>
       <c r="G12" t="n">
-        <v>-9.6759</v>
+        <v>-9.8489</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.9985</v>
+        <v>-5.131699999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.6774</v>
+        <v>-4.717</v>
       </c>
       <c r="J12" t="n">
-        <v>4.619999999999999</v>
+        <v>5.6239</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8257</v>
+        <v>5.427199999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2055999999999997</v>
+        <v>0.1968999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-14.2959</v>
+        <v>-15.4726</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.824199999999998</v>
+        <v>-10.5589</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.4717</v>
+        <v>-4.9138</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.0014</v>
+        <v>-4.8685</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.0041</v>
+        <v>-13.6317</v>
       </c>
       <c r="R12" t="n">
-        <v>9.002599999999999</v>
+        <v>8.763100000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>2.067500000000001</v>
+        <v>2.039700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4016</v>
+        <v>1.5274</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6660999999999997</v>
+        <v>0.512</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3193</v>
+        <v>2.3905</v>
       </c>
       <c r="W12" t="n">
-        <v>6.957800000000001</v>
+        <v>7.1717</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.638500000000001</v>
+        <v>-4.781199999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.8773</v>
+        <v>9.293100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>7.3798</v>
+        <v>8.1272</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4976</v>
+        <v>1.1659</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5379</v>
+        <v>6.5578</v>
       </c>
       <c r="H13" t="n">
-        <v>4.502</v>
+        <v>4.5398</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0359</v>
+        <v>2.018</v>
       </c>
       <c r="J13" t="n">
-        <v>7.1402</v>
+        <v>7.326</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1385</v>
+        <v>5.2753</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0016</v>
+        <v>2.0508</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6022</v>
+        <v>-0.7682</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6365</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P13" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2013</v>
+        <v>-0.7379</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9602000000000001</v>
+        <v>-0.4199</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2411</v>
+        <v>-0.318</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3701</v>
+        <v>5.1357</v>
       </c>
       <c r="E14" t="n">
-        <v>6.353</v>
+        <v>6.6973</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9829</v>
+        <v>-1.5616</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6836</v>
+        <v>4.7634</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1153</v>
+        <v>1.1387</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5683</v>
+        <v>3.6247</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9844</v>
+        <v>6.1712</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3012</v>
+        <v>2.3939</v>
       </c>
       <c r="L14" t="n">
-        <v>3.6833</v>
+        <v>3.7773</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3009</v>
+        <v>-1.4078</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1858</v>
+        <v>-1.2552</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.115</v>
+        <v>-0.1526</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S14" t="n">
-        <v>1.006</v>
+        <v>0.7365</v>
       </c>
       <c r="T14" t="n">
-        <v>0.169</v>
+        <v>0.2787</v>
       </c>
       <c r="U14" t="n">
-        <v>0.837</v>
+        <v>0.4578</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2671</v>
+        <v>3.9807</v>
       </c>
       <c r="E15" t="n">
-        <v>3.292</v>
+        <v>3.0287</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9751</v>
+        <v>0.952</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9575</v>
+        <v>2.9945</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6552</v>
+        <v>1.6929</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3023</v>
+        <v>1.3016</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6012</v>
+        <v>2.6918</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8413</v>
+        <v>1.9218</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7599</v>
+        <v>0.77</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3563</v>
+        <v>0.3027</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1861</v>
+        <v>-0.2289</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3099</v>
+        <v>-0.0401</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4913</v>
+        <v>0.0895</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1814</v>
+        <v>-0.1297</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4476</v>
+        <v>3.8983</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5267</v>
+        <v>3.1277</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.7706</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8818</v>
+        <v>2.9258</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6947</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1871</v>
+        <v>2.1622</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9048</v>
+        <v>3.0586</v>
       </c>
       <c r="K16" t="n">
-        <v>1.545</v>
+        <v>1.6807</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3598</v>
+        <v>1.3779</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.023</v>
+        <v>-0.1328</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.9171</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8273</v>
+        <v>0.7843</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.175</v>
+        <v>-0.6954</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6379</v>
+        <v>-0.2104</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5372</v>
+        <v>-0.485</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>D. FERNANDEZ CANAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4119</v>
+        <v>0.6907</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2867</v>
+        <v>0.5039</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6986</v>
+        <v>0.1868</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4152</v>
+        <v>1.1719</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4991</v>
+        <v>1.775</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9161</v>
+        <v>-0.6031</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7487</v>
+        <v>1.6744</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6016</v>
+        <v>1.5934</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3503</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6665</v>
+        <v>-0.5026</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1007</v>
+        <v>0.1816</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4342</v>
+        <v>-0.6842</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8005</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R17" t="n">
-        <v>2.8008</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7668</v>
+        <v>0.323</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2025</v>
+        <v>0.2178</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5643</v>
+        <v>0.1052</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2598</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2598</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,31 +1813,31 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CANAS</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5806</v>
+        <v>0.457</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5405</v>
+        <v>-1.3745</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04</v>
+        <v>1.8315</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1577</v>
+        <v>-1.4524</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7351</v>
+        <v>-0.5692</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5774</v>
+        <v>-0.8832</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6014</v>
+        <v>-0.6065</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5214</v>
+        <v>0.6492</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08</v>
+        <v>-1.2557</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4437</v>
+        <v>-0.8459</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2138</v>
+        <v>-1.2183</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6574</v>
+        <v>0.3725</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4004</v>
+        <v>1.7526</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0006</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6002</v>
+        <v>2.7263</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3037</v>
+        <v>-0.1228</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4202</v>
+        <v>-0.0738</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1165</v>
+        <v>-0.0489</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5196</v>
+        <v>0.2795</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5196</v>
+        <v>0.2795</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0028</v>
+        <v>0.1214</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8031</v>
+        <v>-0.5394</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8003</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5249</v>
+        <v>-0.4953</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7228</v>
+        <v>-1.6867</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1979</v>
+        <v>1.1913</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6742</v>
+        <v>-0.6151</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.994</v>
+        <v>-1.9525</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3198</v>
+        <v>1.3374</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S20" t="n">
-        <v>0.322</v>
+        <v>0.422</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1289</v>
+        <v>0.0757</v>
       </c>
       <c r="U20" t="n">
-        <v>0.451</v>
+        <v>0.3463</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1891</v>
+        <v>-1.2132</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1064</v>
+        <v>0.0509</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2955</v>
+        <v>-1.2642</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3719</v>
+        <v>0.3177</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1774</v>
+        <v>-0.2073</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8799</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8105</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.508</v>
+        <v>-0.5749</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2574</v>
+        <v>-0.2895</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S21" t="n">
-        <v>0.239</v>
+        <v>0.2743</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2268</v>
+        <v>0.132</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0122</v>
+        <v>0.1424</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2244</v>
+        <v>-1.5296</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4894</v>
+        <v>-1.8516</v>
       </c>
       <c r="F22" t="n">
-        <v>0.265</v>
+        <v>0.322</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8315</v>
+        <v>-1.8109</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0179</v>
+        <v>-1.0135</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8136</v>
+        <v>-0.7974</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.974</v>
+        <v>-1.9319</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.618</v>
+        <v>-0.6029</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.356</v>
+        <v>-1.329</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1425</v>
+        <v>0.1211</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S22" t="n">
-        <v>0.407</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4846</v>
+        <v>0.0803</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0776</v>
+        <v>0.0062</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9778</v>
+        <v>-1.7715</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6428</v>
+        <v>-1.4988</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3351</v>
+        <v>-0.2727</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8355</v>
+        <v>-0.8418</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5224</v>
+        <v>-0.5111</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3131</v>
+        <v>-0.3308</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.578</v>
+        <v>-0.5629</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.658</v>
+        <v>-0.644</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2575</v>
+        <v>-0.2789</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.142</v>
+        <v>0.0441</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0645</v>
+        <v>0.0378</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0776</v>
+        <v>0.0062</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8505</v>
+        <v>-2.8945</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2507</v>
+        <v>-2.3904</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5998</v>
+        <v>-0.5042</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9846</v>
+        <v>-1.9822</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0822</v>
+        <v>-1.0858</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9023</v>
+        <v>-0.8963</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0905</v>
+        <v>-0.9782999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9056</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1162</v>
+        <v>-0.0727</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8941</v>
+        <v>-1.0038</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1079</v>
+        <v>-0.1802</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7862</v>
+        <v>-0.8236</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2063</v>
+        <v>-1.2171</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1599</v>
+        <v>-0.4384</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0464</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.019</v>
+        <v>-6.489</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0596</v>
+        <v>-3.5103</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9594</v>
+        <v>-2.9786</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9226</v>
+        <v>-2.9077</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3181</v>
+        <v>0.295</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.2407</v>
+        <v>-3.2027</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.3503</v>
+        <v>-2.2552</v>
       </c>
       <c r="K25" t="n">
-        <v>1.0397</v>
+        <v>1.0674</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.39</v>
+        <v>-3.3225</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5723</v>
+        <v>-0.6526</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7216</v>
+        <v>-0.7723</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6971</v>
+        <v>-1.1128</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.709</v>
+        <v>-0.2815</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9881</v>
+        <v>-0.8313</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.2909</v>
+        <v>10.287</v>
       </c>
       <c r="E26" t="n">
-        <v>9.266000000000002</v>
+        <v>10.9786</v>
       </c>
       <c r="F26" t="n">
-        <v>1.024799999999999</v>
+        <v>-0.6916999999999995</v>
       </c>
       <c r="G26" t="n">
-        <v>9.675999999999998</v>
+        <v>9.848700000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>4.998600000000001</v>
+        <v>5.131399999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>4.677499999999998</v>
+        <v>4.717200000000002</v>
       </c>
       <c r="J26" t="n">
-        <v>14.2961</v>
+        <v>15.4726</v>
       </c>
       <c r="K26" t="n">
-        <v>9.824400000000001</v>
+        <v>10.5588</v>
       </c>
       <c r="L26" t="n">
-        <v>4.471700000000002</v>
+        <v>4.914099999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.6201</v>
+        <v>-5.623899999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.8256</v>
+        <v>-5.427099999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2057</v>
+        <v>-0.1966999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>5.0015</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.002699999999999</v>
+        <v>-8.763300000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>14.0041</v>
+        <v>13.6315</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0673</v>
+        <v>-2.0397</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6659999999999999</v>
+        <v>-0.5122</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.4014</v>
+        <v>-1.5275</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.3192</v>
+        <v>-2.3905</v>
       </c>
       <c r="W26" t="n">
-        <v>4.6386</v>
+        <v>4.7813</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.9578</v>
+        <v>-7.1717</v>
       </c>
     </row>
   </sheetData>
